--- a/docs/tableau_competences.xlsx
+++ b/docs/tableau_competences.xlsx
@@ -45,7 +45,24 @@
     <t xml:space="preserve"> X SLAM</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : roudard.fr</t>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <sz val="18.0"/>
+      </rPr>
+      <t xml:space="preserve">Adresse URL du portfolio : </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial"/>
+        <b/>
+        <color rgb="FF1155CC"/>
+        <sz val="18.0"/>
+        <u/>
+      </rPr>
+      <t>https://ryanthao.github.io/PORTFOLIO/</t>
+    </r>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -199,7 +216,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -222,6 +239,13 @@
     <font>
       <sz val="10.0"/>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18.0"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -595,21 +619,21 @@
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="12" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="13" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="16" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="17" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="17" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -620,71 +644,71 @@
     <xf borderId="21" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" textRotation="90" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="22" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="24" fillId="2" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="24" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="23" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="22" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="23" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="23" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="24" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="23" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="22" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="23" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="24" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="25" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="15" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="25" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="15" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1139,7 +1163,7 @@
       <c r="G16" s="31"/>
       <c r="H16" s="32"/>
     </row>
-    <row r="17" ht="12.75" customHeight="1">
+    <row r="17" ht="35.25" customHeight="1">
       <c r="A17" s="36" t="s">
         <v>40</v>
       </c>
@@ -10976,9 +11000,12 @@
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A5"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins bottom="0.1968503937007874" footer="0.0" header="0.0" left="0.1968503937007874" right="0.1968503937007874" top="0.1968503937007874"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>